--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run2/epoch_40/per_file_predictions_epoch_40.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run2/epoch_40/per_file_predictions_epoch_40.xlsx
@@ -808,766 +808,766 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9790,0.0026,0.0193,0.0008</t>
-  </si>
-  <si>
-    <t>0.0095,0.0003,0.0001,0.9978</t>
-  </si>
-  <si>
-    <t>0.4305,0.0015,0.0008,0.8153</t>
-  </si>
-  <si>
-    <t>0.0790,0.0009,0.0008,0.9815</t>
-  </si>
-  <si>
-    <t>0.9985,0.0004,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0001,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9982,0.0003,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0000,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9970,0.0008,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9857,0.0140,0.0010,0.0009</t>
-  </si>
-  <si>
-    <t>0.9986,0.0003,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9985,0.0003,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.4732,0.4056,0.1845,0.0055</t>
-  </si>
-  <si>
-    <t>0.0065,0.0270,0.9816,0.0027</t>
-  </si>
-  <si>
-    <t>0.6047,0.0046,0.6769,0.0002</t>
-  </si>
-  <si>
-    <t>0.0079,0.0033,0.9879,0.0024</t>
-  </si>
-  <si>
-    <t>0.9800,0.0046,0.0143,0.0006</t>
-  </si>
-  <si>
-    <t>0.0011,0.9966,0.0011,0.0004</t>
-  </si>
-  <si>
-    <t>0.0038,0.9918,0.0186,0.0003</t>
-  </si>
-  <si>
-    <t>0.1702,0.8871,0.0031,0.0008</t>
-  </si>
-  <si>
-    <t>0.0072,0.9887,0.0059,0.0001</t>
-  </si>
-  <si>
-    <t>0.0016,0.9965,0.0031,0.0001</t>
-  </si>
-  <si>
-    <t>0.4324,0.0031,0.7052,0.0014</t>
-  </si>
-  <si>
-    <t>0.7978,0.0098,0.2606,0.0029</t>
-  </si>
-  <si>
-    <t>0.0062,0.0016,0.9890,0.0016</t>
-  </si>
-  <si>
-    <t>0.0141,0.0023,0.9903,0.0002</t>
-  </si>
-  <si>
-    <t>0.0200,0.0070,0.9704,0.0068</t>
-  </si>
-  <si>
-    <t>0.0105,0.0015,0.9881,0.0005</t>
-  </si>
-  <si>
-    <t>0.0011,0.0005,0.9964,0.0008</t>
-  </si>
-  <si>
-    <t>0.8815,0.1623,0.0078,0.0004</t>
-  </si>
-  <si>
-    <t>0.2823,0.5149,0.3376,0.0201</t>
-  </si>
-  <si>
-    <t>0.0197,0.0558,0.9578,0.0175</t>
-  </si>
-  <si>
-    <t>0.0152,0.7813,0.3785,0.0028</t>
-  </si>
-  <si>
-    <t>0.9473,0.0132,0.0099,0.0180</t>
-  </si>
-  <si>
-    <t>0.8564,0.0323,0.1420,0.0082</t>
-  </si>
-  <si>
-    <t>0.3303,0.8104,0.0072,0.0011</t>
-  </si>
-  <si>
-    <t>0.0414,0.9468,0.0755,0.0037</t>
-  </si>
-  <si>
-    <t>0.0298,0.5726,0.5389,0.0316</t>
-  </si>
-  <si>
-    <t>0.5339,0.0061,0.5571,0.0062</t>
-  </si>
-  <si>
-    <t>0.0235,0.0070,0.9700,0.0040</t>
-  </si>
-  <si>
-    <t>0.0371,0.0044,0.9649,0.0024</t>
-  </si>
-  <si>
-    <t>0.0321,0.0529,0.9671,0.0009</t>
-  </si>
-  <si>
-    <t>0.0236,0.8942,0.0679,0.0048</t>
-  </si>
-  <si>
-    <t>0.0168,0.0048,0.9727,0.0061</t>
-  </si>
-  <si>
-    <t>0.2562,0.0393,0.0357,0.8075</t>
-  </si>
-  <si>
-    <t>0.0028,0.9875,0.0027,0.0048</t>
-  </si>
-  <si>
-    <t>0.0168,0.9663,0.0265,0.0036</t>
-  </si>
-  <si>
-    <t>0.0039,0.9888,0.0116,0.0017</t>
-  </si>
-  <si>
-    <t>0.0043,0.0335,0.9859,0.0053</t>
-  </si>
-  <si>
-    <t>0.0049,0.1573,0.9784,0.0031</t>
-  </si>
-  <si>
-    <t>0.0196,0.0080,0.9746,0.0024</t>
-  </si>
-  <si>
-    <t>0.0442,0.0006,0.9692,0.0009</t>
-  </si>
-  <si>
-    <t>0.0108,0.0119,0.9848,0.0010</t>
-  </si>
-  <si>
-    <t>0.0129,0.0041,0.9881,0.0002</t>
-  </si>
-  <si>
-    <t>0.9745,0.0161,0.0082,0.0009</t>
-  </si>
-  <si>
-    <t>0.9883,0.0034,0.0010,0.0029</t>
-  </si>
-  <si>
-    <t>0.9965,0.0009,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.0062,0.0032,0.9872,0.0075</t>
-  </si>
-  <si>
-    <t>0.9916,0.0037,0.0019,0.0006</t>
-  </si>
-  <si>
-    <t>0.9944,0.0032,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9954,0.0045,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0091,0.7254,0.9218,0.0044</t>
-  </si>
-  <si>
-    <t>0.0054,0.0008,0.9931,0.0009</t>
-  </si>
-  <si>
-    <t>0.0087,0.0968,0.9231,0.0436</t>
-  </si>
-  <si>
-    <t>0.0014,0.9517,0.9566,0.0004</t>
-  </si>
-  <si>
-    <t>0.0009,0.0008,0.9922,0.0194</t>
-  </si>
-  <si>
-    <t>0.0100,0.9839,0.0044,0.0004</t>
-  </si>
-  <si>
-    <t>0.0061,0.9936,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9866,0.0042,0.0045,0.0013</t>
-  </si>
-  <si>
-    <t>0.0407,0.0211,0.9635,0.0064</t>
-  </si>
-  <si>
-    <t>0.0298,0.0473,0.9748,0.0022</t>
-  </si>
-  <si>
-    <t>0.0044,0.9203,0.7906,0.0017</t>
-  </si>
-  <si>
-    <t>0.0034,0.9264,0.6003,0.0006</t>
-  </si>
-  <si>
-    <t>0.0154,0.9533,0.1818,0.0041</t>
-  </si>
-  <si>
-    <t>0.0026,0.8577,0.9595,0.0013</t>
-  </si>
-  <si>
-    <t>0.0021,0.0002,0.0090,0.9967</t>
-  </si>
-  <si>
-    <t>0.0007,0.0009,0.0033,0.9985</t>
-  </si>
-  <si>
-    <t>0.0195,0.0075,0.0012,0.9901</t>
-  </si>
-  <si>
-    <t>0.0110,0.0004,0.0025,0.9949</t>
-  </si>
-  <si>
-    <t>0.0231,0.0017,0.0136,0.9838</t>
-  </si>
-  <si>
-    <t>0.0018,0.0096,0.0006,0.9978</t>
-  </si>
-  <si>
-    <t>0.0506,0.7358,0.6355,0.0249</t>
-  </si>
-  <si>
-    <t>0.0276,0.3330,0.9067,0.0008</t>
-  </si>
-  <si>
-    <t>0.0085,0.8422,0.8516,0.0027</t>
-  </si>
-  <si>
-    <t>0.0036,0.6841,0.9666,0.0005</t>
-  </si>
-  <si>
-    <t>0.0041,0.9654,0.6020,0.0002</t>
-  </si>
-  <si>
-    <t>0.0027,0.9367,0.7043,0.0007</t>
-  </si>
-  <si>
-    <t>0.9984,0.0004,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9966,0.0015,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9906,0.0115,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9982,0.0001,0.0000,0.0009</t>
-  </si>
-  <si>
-    <t>0.9931,0.0024,0.0001,0.0010</t>
-  </si>
-  <si>
-    <t>0.9989,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9978,0.0006,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9982,0.0004,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0003,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0000,0.0000,0.0002</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.9894,0.0013,0.0028,0.0011</t>
+  </si>
+  <si>
+    <t>0.0045,0.0014,0.0003,0.9977</t>
+  </si>
+  <si>
+    <t>0.7763,0.0085,0.0023,0.2694</t>
+  </si>
+  <si>
+    <t>0.1233,0.0011,0.0015,0.9568</t>
+  </si>
+  <si>
+    <t>0.9965,0.0016,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9983,0.0006,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9965,0.0013,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0000,0.0002</t>
   </si>
   <si>
     <t>0.9991,0.0002,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.9931,0.0050,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9976,0.0002,0.0001,0.0010</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.0085,0.0010,0.9909,0.0010</t>
-  </si>
-  <si>
-    <t>0.0218,0.0032,0.9736,0.0025</t>
-  </si>
-  <si>
-    <t>0.9702,0.0008,0.0284,0.0007</t>
-  </si>
-  <si>
-    <t>0.0053,0.0011,0.9933,0.0007</t>
-  </si>
-  <si>
-    <t>0.0037,0.9929,0.0097,0.0004</t>
-  </si>
-  <si>
-    <t>0.0235,0.9705,0.0092,0.0009</t>
-  </si>
-  <si>
-    <t>0.0196,0.9803,0.0077,0.0010</t>
-  </si>
-  <si>
-    <t>0.0046,0.9887,0.0021,0.0060</t>
-  </si>
-  <si>
-    <t>0.0042,0.9924,0.0031,0.0008</t>
-  </si>
-  <si>
-    <t>0.0021,0.9951,0.0036,0.0010</t>
-  </si>
-  <si>
-    <t>0.3555,0.7519,0.0019,0.0013</t>
-  </si>
-  <si>
-    <t>0.5087,0.2064,0.4335,0.0485</t>
-  </si>
-  <si>
-    <t>0.1698,0.0034,0.8901,0.0027</t>
-  </si>
-  <si>
-    <t>0.6104,0.0677,0.4105,0.0069</t>
-  </si>
-  <si>
-    <t>0.5633,0.0302,0.6049,0.0045</t>
-  </si>
-  <si>
-    <t>0.5214,0.0467,0.1438,0.3538</t>
-  </si>
-  <si>
-    <t>0.0030,0.9900,0.0018,0.0034</t>
-  </si>
-  <si>
-    <t>0.0057,0.9873,0.0028,0.0012</t>
-  </si>
-  <si>
-    <t>0.0061,0.9793,0.0116,0.0115</t>
-  </si>
-  <si>
-    <t>0.0016,0.9858,0.6182,0.0004</t>
-  </si>
-  <si>
-    <t>0.0065,0.9855,0.0323,0.0001</t>
-  </si>
-  <si>
-    <t>0.3887,0.7737,0.0083,0.0013</t>
-  </si>
-  <si>
-    <t>0.5043,0.6589,0.0148,0.0009</t>
-  </si>
-  <si>
-    <t>0.9956,0.0019,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9969,0.0007,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9975,0.0004,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9943,0.0009,0.0000,0.0015</t>
-  </si>
-  <si>
-    <t>0.9977,0.0002,0.0017,0.0001</t>
-  </si>
-  <si>
-    <t>0.9956,0.0013,0.0004,0.0006</t>
-  </si>
-  <si>
-    <t>0.9987,0.0001,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.0076,0.6618,0.9223,0.0016</t>
-  </si>
-  <si>
-    <t>0.0137,0.5897,0.9141,0.0027</t>
-  </si>
-  <si>
-    <t>0.0196,0.0502,0.9773,0.0001</t>
-  </si>
-  <si>
-    <t>0.2504,0.0222,0.8005,0.0054</t>
-  </si>
-  <si>
-    <t>0.9884,0.0016,0.0033,0.0008</t>
-  </si>
-  <si>
-    <t>0.8721,0.0072,0.2030,0.0027</t>
-  </si>
-  <si>
-    <t>0.2446,0.0027,0.8351,0.0046</t>
-  </si>
-  <si>
-    <t>0.9277,0.0091,0.0593,0.0081</t>
-  </si>
-  <si>
-    <t>0.0653,0.0008,0.0004,0.9824</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.0047,0.9995</t>
-  </si>
-  <si>
-    <t>0.0029,0.0004,0.0010,0.9982</t>
-  </si>
-  <si>
-    <t>0.0213,0.0001,0.0003,0.9952</t>
-  </si>
-  <si>
-    <t>0.0141,0.5028,0.7486,0.0136</t>
-  </si>
-  <si>
-    <t>0.9941,0.0028,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.1694,0.8785,0.0043,0.0024</t>
-  </si>
-  <si>
-    <t>0.9972,0.0003,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.7847,0.3397,0.0068,0.0010</t>
-  </si>
-  <si>
-    <t>0.9892,0.0020,0.0020,0.0024</t>
-  </si>
-  <si>
-    <t>0.1069,0.0009,0.0312,0.8707</t>
-  </si>
-  <si>
-    <t>0.9871,0.0026,0.0029,0.0029</t>
-  </si>
-  <si>
-    <t>0.0015,0.0628,0.9908,0.0084</t>
-  </si>
-  <si>
-    <t>0.5902,0.0000,0.0001,0.7523</t>
-  </si>
-  <si>
-    <t>0.9504,0.0010,0.0015,0.0558</t>
-  </si>
-  <si>
-    <t>0.2290,0.7300,0.0708,0.0132</t>
-  </si>
-  <si>
-    <t>0.9662,0.0102,0.0179,0.0033</t>
-  </si>
-  <si>
-    <t>0.9688,0.0252,0.0081,0.0010</t>
-  </si>
-  <si>
-    <t>0.2950,0.6323,0.1825,0.0410</t>
-  </si>
-  <si>
-    <t>0.6444,0.1490,0.3294,0.0052</t>
-  </si>
-  <si>
-    <t>0.9503,0.0402,0.0120,0.0017</t>
-  </si>
-  <si>
-    <t>0.9986,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9977,0.0005,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9966,0.0011,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.9981,0.0002,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9969,0.0002,0.0002,0.0015</t>
-  </si>
-  <si>
-    <t>0.9942,0.0019,0.0012,0.0007</t>
-  </si>
-  <si>
-    <t>0.9977,0.0003,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9989,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.7583,0.3210,0.0259,0.0026</t>
-  </si>
-  <si>
-    <t>0.5129,0.5768,0.0129,0.0023</t>
-  </si>
-  <si>
-    <t>0.3501,0.7738,0.0020,0.0006</t>
-  </si>
-  <si>
-    <t>0.9373,0.0608,0.0128,0.0015</t>
-  </si>
-  <si>
-    <t>0.9933,0.0057,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9895,0.0049,0.0014,0.0011</t>
-  </si>
-  <si>
-    <t>0.9956,0.0019,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.9891,0.0079,0.0013,0.0004</t>
-  </si>
-  <si>
-    <t>0.0030,0.0057,0.9962,0.0005</t>
-  </si>
-  <si>
-    <t>0.9567,0.0283,0.0018,0.0048</t>
-  </si>
-  <si>
-    <t>0.0035,0.0010,0.9956,0.0001</t>
-  </si>
-  <si>
-    <t>0.0043,0.0272,0.9864,0.0032</t>
-  </si>
-  <si>
-    <t>0.0015,0.0011,0.9967,0.0008</t>
-  </si>
-  <si>
-    <t>0.0217,0.0115,0.9767,0.0020</t>
-  </si>
-  <si>
-    <t>0.0047,0.0146,0.9881,0.0024</t>
-  </si>
-  <si>
-    <t>0.0030,0.0010,0.9961,0.0003</t>
-  </si>
-  <si>
-    <t>0.0077,0.0014,0.9904,0.0009</t>
-  </si>
-  <si>
-    <t>0.0146,0.0097,0.9822,0.0019</t>
-  </si>
-  <si>
-    <t>0.4978,0.0027,0.7185,0.0018</t>
-  </si>
-  <si>
-    <t>0.2129,0.0232,0.7920,0.0365</t>
-  </si>
-  <si>
-    <t>0.1170,0.0193,0.9221,0.0011</t>
-  </si>
-  <si>
-    <t>0.2767,0.0649,0.7548,0.0077</t>
-  </si>
-  <si>
-    <t>0.5045,0.0305,0.6164,0.0035</t>
-  </si>
-  <si>
-    <t>0.4956,0.0207,0.7134,0.0033</t>
-  </si>
-  <si>
-    <t>0.2801,0.0323,0.8216,0.0069</t>
-  </si>
-  <si>
-    <t>0.6272,0.4900,0.0137,0.0002</t>
-  </si>
-  <si>
-    <t>0.2781,0.8264,0.0045,0.0009</t>
-  </si>
-  <si>
-    <t>0.8338,0.3034,0.0035,0.0002</t>
-  </si>
-  <si>
-    <t>0.9901,0.0101,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9184,0.2139,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.5921,0.2752,0.1990,0.0198</t>
-  </si>
-  <si>
-    <t>0.9681,0.0019,0.0230,0.0014</t>
-  </si>
-  <si>
-    <t>0.9192,0.0026,0.0394,0.0106</t>
-  </si>
-  <si>
-    <t>0.5576,0.0041,0.6220,0.0021</t>
-  </si>
-  <si>
-    <t>0.8441,0.0017,0.2851,0.0011</t>
-  </si>
-  <si>
-    <t>0.0148,0.0381,0.9651,0.0149</t>
-  </si>
-  <si>
-    <t>0.0544,0.1309,0.9051,0.0025</t>
-  </si>
-  <si>
-    <t>0.0509,0.1440,0.8952,0.0007</t>
-  </si>
-  <si>
-    <t>0.1275,0.0136,0.9105,0.0013</t>
-  </si>
-  <si>
-    <t>0.0068,0.0172,0.9677,0.0153</t>
-  </si>
-  <si>
-    <t>0.9959,0.0012,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9959,0.0006,0.0009,0.0009</t>
-  </si>
-  <si>
-    <t>0.9949,0.0022,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9981,0.0014,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9954,0.0010,0.0001,0.0016</t>
-  </si>
-  <si>
-    <t>0.9967,0.0011,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9970,0.0007,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9968,0.0002,0.0002,0.0016</t>
-  </si>
-  <si>
-    <t>0.0071,0.0010,0.9906,0.0016</t>
-  </si>
-  <si>
-    <t>0.3084,0.0439,0.7524,0.0405</t>
-  </si>
-  <si>
-    <t>0.6103,0.0050,0.2696,0.0560</t>
-  </si>
-  <si>
-    <t>0.0143,0.0105,0.9851,0.0010</t>
-  </si>
-  <si>
-    <t>0.0033,0.0035,0.9922,0.0016</t>
-  </si>
-  <si>
-    <t>0.0632,0.0264,0.9297,0.0035</t>
-  </si>
-  <si>
-    <t>0.0134,0.0058,0.9830,0.0019</t>
-  </si>
-  <si>
-    <t>0.0020,0.0067,0.9915,0.0057</t>
-  </si>
-  <si>
-    <t>0.0039,0.0030,0.9922,0.0018</t>
-  </si>
-  <si>
-    <t>0.0525,0.0066,0.9590,0.0014</t>
-  </si>
-  <si>
-    <t>0.1040,0.0827,0.8405,0.0354</t>
-  </si>
-  <si>
-    <t>0.6379,0.0115,0.5118,0.0030</t>
-  </si>
-  <si>
-    <t>0.8277,0.0034,0.2507,0.0019</t>
-  </si>
-  <si>
-    <t>0.4843,0.0189,0.6231,0.0163</t>
-  </si>
-  <si>
-    <t>0.9960,0.0017,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9971,0.0008,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9983,0.0006,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9910,0.0046,0.0005,0.0013</t>
-  </si>
-  <si>
-    <t>0.9963,0.0011,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9858,0.0147,0.0008,0.0010</t>
-  </si>
-  <si>
-    <t>0.9980,0.0008,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9966,0.0004,0.0001,0.0014</t>
-  </si>
-  <si>
-    <t>0.0683,0.0034,0.9570,0.0002</t>
-  </si>
-  <si>
-    <t>0.0038,0.0361,0.9821,0.0058</t>
-  </si>
-  <si>
-    <t>0.0273,0.0229,0.9713,0.0020</t>
-  </si>
-  <si>
-    <t>0.0076,0.0229,0.9797,0.0051</t>
-  </si>
-  <si>
-    <t>0.0063,0.0037,0.9906,0.0010</t>
-  </si>
-  <si>
-    <t>0.0047,0.0019,0.9870,0.0083</t>
-  </si>
-  <si>
-    <t>0.0645,0.0028,0.9568,0.0020</t>
-  </si>
-  <si>
-    <t>0.2977,0.0163,0.7418,0.0084</t>
-  </si>
-  <si>
-    <t>0.6845,0.0011,0.0148,0.2430</t>
-  </si>
-  <si>
-    <t>0.0578,0.0206,0.0044,0.9658</t>
-  </si>
-  <si>
-    <t>0.0138,0.0024,0.0018,0.9930</t>
-  </si>
-  <si>
-    <t>0.0073,0.0002,0.0030,0.9955</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.0007,0.9997</t>
-  </si>
-  <si>
-    <t>0.8857,0.0021,0.0031,0.1367</t>
+    <t>0.3036,0.0178,0.8408,0.0010</t>
+  </si>
+  <si>
+    <t>0.0748,0.0090,0.9527,0.0009</t>
+  </si>
+  <si>
+    <t>0.1721,0.0045,0.9366,0.0001</t>
+  </si>
+  <si>
+    <t>0.0449,0.0065,0.9552,0.0062</t>
+  </si>
+  <si>
+    <t>0.9774,0.0063,0.0147,0.0008</t>
+  </si>
+  <si>
+    <t>0.0010,0.9970,0.0041,0.0003</t>
+  </si>
+  <si>
+    <t>0.0032,0.9932,0.0021,0.0003</t>
+  </si>
+  <si>
+    <t>0.1282,0.8923,0.0092,0.0023</t>
+  </si>
+  <si>
+    <t>0.0104,0.9863,0.0119,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.9987,0.0054,0.0000</t>
+  </si>
+  <si>
+    <t>0.7060,0.0133,0.3096,0.0134</t>
+  </si>
+  <si>
+    <t>0.5547,0.0057,0.5924,0.0022</t>
+  </si>
+  <si>
+    <t>0.0029,0.0006,0.9948,0.0007</t>
+  </si>
+  <si>
+    <t>0.0669,0.0036,0.9586,0.0010</t>
+  </si>
+  <si>
+    <t>0.0297,0.0024,0.9742,0.0016</t>
+  </si>
+  <si>
+    <t>0.1751,0.0034,0.9046,0.0016</t>
+  </si>
+  <si>
+    <t>0.0017,0.0007,0.9918,0.0057</t>
+  </si>
+  <si>
+    <t>0.9615,0.0490,0.0075,0.0002</t>
+  </si>
+  <si>
+    <t>0.8291,0.0336,0.1691,0.0145</t>
+  </si>
+  <si>
+    <t>0.0216,0.0481,0.9631,0.0117</t>
+  </si>
+  <si>
+    <t>0.2720,0.3541,0.2157,0.0041</t>
+  </si>
+  <si>
+    <t>0.8923,0.0267,0.0195,0.0581</t>
+  </si>
+  <si>
+    <t>0.8578,0.1692,0.0236,0.0064</t>
+  </si>
+  <si>
+    <t>0.5383,0.6315,0.0179,0.0022</t>
+  </si>
+  <si>
+    <t>0.0194,0.9615,0.0828,0.0051</t>
+  </si>
+  <si>
+    <t>0.0428,0.5789,0.5526,0.0395</t>
+  </si>
+  <si>
+    <t>0.1109,0.0055,0.8924,0.0099</t>
+  </si>
+  <si>
+    <t>0.2880,0.0079,0.8343,0.0018</t>
+  </si>
+  <si>
+    <t>0.1662,0.0055,0.8704,0.0030</t>
+  </si>
+  <si>
+    <t>0.0246,0.0300,0.9779,0.0007</t>
+  </si>
+  <si>
+    <t>0.0059,0.9896,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.0021,0.0024,0.9886,0.0154</t>
+  </si>
+  <si>
+    <t>0.3702,0.0742,0.0127,0.6664</t>
+  </si>
+  <si>
+    <t>0.0070,0.9829,0.0033,0.0018</t>
+  </si>
+  <si>
+    <t>0.0270,0.9505,0.0426,0.0019</t>
+  </si>
+  <si>
+    <t>0.0014,0.9919,0.0028,0.0018</t>
+  </si>
+  <si>
+    <t>0.0035,0.0121,0.9909,0.0023</t>
+  </si>
+  <si>
+    <t>0.0111,0.1345,0.9586,0.0044</t>
+  </si>
+  <si>
+    <t>0.0277,0.0080,0.9667,0.0041</t>
+  </si>
+  <si>
+    <t>0.0080,0.0011,0.9917,0.0009</t>
+  </si>
+  <si>
+    <t>0.0066,0.0073,0.9908,0.0008</t>
+  </si>
+  <si>
+    <t>0.0120,0.0017,0.9914,0.0001</t>
+  </si>
+  <si>
+    <t>0.9875,0.0112,0.0007,0.0009</t>
+  </si>
+  <si>
+    <t>0.9934,0.0033,0.0016,0.0003</t>
+  </si>
+  <si>
+    <t>0.9974,0.0004,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.0242,0.0062,0.9749,0.0064</t>
+  </si>
+  <si>
+    <t>0.9951,0.0016,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9871,0.0141,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.0044,0.7012,0.9558,0.0020</t>
+  </si>
+  <si>
+    <t>0.0082,0.0010,0.9897,0.0014</t>
+  </si>
+  <si>
+    <t>0.0126,0.1039,0.8926,0.0317</t>
+  </si>
+  <si>
+    <t>0.0018,0.8704,0.9756,0.0005</t>
+  </si>
+  <si>
+    <t>0.0017,0.0007,0.9947,0.0026</t>
+  </si>
+  <si>
+    <t>0.0057,0.9919,0.0035,0.0001</t>
+  </si>
+  <si>
+    <t>0.0136,0.9894,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9789,0.0054,0.0161,0.0007</t>
+  </si>
+  <si>
+    <t>0.1283,0.0590,0.8976,0.0061</t>
+  </si>
+  <si>
+    <t>0.0149,0.0202,0.9830,0.0028</t>
+  </si>
+  <si>
+    <t>0.0022,0.9678,0.4040,0.0039</t>
+  </si>
+  <si>
+    <t>0.0058,0.9448,0.2096,0.0005</t>
+  </si>
+  <si>
+    <t>0.0009,0.9943,0.2857,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.8336,0.9756,0.0005</t>
+  </si>
+  <si>
+    <t>0.0041,0.0004,0.0169,0.9939</t>
+  </si>
+  <si>
+    <t>0.0014,0.0030,0.0004,0.9985</t>
+  </si>
+  <si>
+    <t>0.0161,0.0005,0.0005,0.9947</t>
+  </si>
+  <si>
+    <t>0.0575,0.0008,0.0010,0.9854</t>
+  </si>
+  <si>
+    <t>0.0066,0.0007,0.0017,0.9960</t>
+  </si>
+  <si>
+    <t>0.0010,0.0030,0.0003,0.9989</t>
+  </si>
+  <si>
+    <t>0.0119,0.8023,0.8177,0.0021</t>
+  </si>
+  <si>
+    <t>0.0103,0.8175,0.8732,0.0008</t>
+  </si>
+  <si>
+    <t>0.0265,0.2855,0.8888,0.0010</t>
+  </si>
+  <si>
+    <t>0.0017,0.9405,0.8971,0.0001</t>
+  </si>
+  <si>
+    <t>0.0030,0.9604,0.7504,0.0003</t>
+  </si>
+  <si>
+    <t>0.0066,0.9089,0.5155,0.0004</t>
+  </si>
+  <si>
+    <t>0.9975,0.0006,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9950,0.0043,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9945,0.0057,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0005,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9986,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9910,0.0081,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9916,0.0050,0.0006,0.0009</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9979,0.0010,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9956,0.0027,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.0022,0.0003,0.9959,0.0019</t>
+  </si>
+  <si>
+    <t>0.0047,0.0043,0.9912,0.0012</t>
+  </si>
+  <si>
+    <t>0.9834,0.0005,0.0142,0.0003</t>
+  </si>
+  <si>
+    <t>0.0057,0.0006,0.9936,0.0006</t>
+  </si>
+  <si>
+    <t>0.0065,0.9869,0.0091,0.0019</t>
+  </si>
+  <si>
+    <t>0.0031,0.9942,0.0044,0.0006</t>
+  </si>
+  <si>
+    <t>0.3186,0.7643,0.0330,0.0005</t>
+  </si>
+  <si>
+    <t>0.0213,0.9727,0.0037,0.0045</t>
+  </si>
+  <si>
+    <t>0.0367,0.9616,0.0126,0.0016</t>
+  </si>
+  <si>
+    <t>0.0114,0.9837,0.0067,0.0007</t>
+  </si>
+  <si>
+    <t>0.1733,0.8616,0.0025,0.0038</t>
+  </si>
+  <si>
+    <t>0.1089,0.1263,0.8511,0.0339</t>
+  </si>
+  <si>
+    <t>0.8764,0.0110,0.1227,0.0052</t>
+  </si>
+  <si>
+    <t>0.6436,0.0785,0.3912,0.0036</t>
+  </si>
+  <si>
+    <t>0.6051,0.0445,0.5146,0.0073</t>
+  </si>
+  <si>
+    <t>0.0389,0.0797,0.0691,0.9405</t>
+  </si>
+  <si>
+    <t>0.0023,0.9934,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.0024,0.9951,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.0043,0.9719,0.0088,0.0703</t>
+  </si>
+  <si>
+    <t>0.0021,0.9783,0.7857,0.0007</t>
+  </si>
+  <si>
+    <t>0.0044,0.9927,0.0107,0.0002</t>
+  </si>
+  <si>
+    <t>0.1917,0.8559,0.0307,0.0046</t>
+  </si>
+  <si>
+    <t>0.8418,0.2203,0.0279,0.0012</t>
+  </si>
+  <si>
+    <t>0.9976,0.0002,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9983,0.0002,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9980,0.0002,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9969,0.0008,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9983,0.0001,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9969,0.0009,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9910,0.0045,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9979,0.0007,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0041,0.3584,0.9537,0.0066</t>
+  </si>
+  <si>
+    <t>0.0084,0.5175,0.9556,0.0012</t>
+  </si>
+  <si>
+    <t>0.0290,0.0389,0.9726,0.0001</t>
+  </si>
+  <si>
+    <t>0.0083,0.0013,0.9861,0.0020</t>
+  </si>
+  <si>
+    <t>0.9761,0.0014,0.0120,0.0018</t>
+  </si>
+  <si>
+    <t>0.0485,0.0066,0.9588,0.0026</t>
+  </si>
+  <si>
+    <t>0.0902,0.0006,0.9533,0.0010</t>
+  </si>
+  <si>
+    <t>0.7684,0.0185,0.3318,0.0037</t>
+  </si>
+  <si>
+    <t>0.3369,0.0004,0.0004,0.8854</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.0721,0.9977</t>
+  </si>
+  <si>
+    <t>0.0033,0.0017,0.0005,0.9980</t>
+  </si>
+  <si>
+    <t>0.0234,0.0003,0.0023,0.9896</t>
+  </si>
+  <si>
+    <t>0.0378,0.6527,0.5019,0.0058</t>
+  </si>
+  <si>
+    <t>0.9965,0.0011,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.0063,0.9877,0.0007,0.0042</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.7178,0.3567,0.0133,0.0022</t>
+  </si>
+  <si>
+    <t>0.9956,0.0006,0.0008,0.0010</t>
+  </si>
+  <si>
+    <t>0.8086,0.0021,0.0148,0.1654</t>
+  </si>
+  <si>
+    <t>0.9924,0.0014,0.0018,0.0016</t>
+  </si>
+  <si>
+    <t>0.0019,0.0390,0.9905,0.0106</t>
+  </si>
+  <si>
+    <t>0.9757,0.0005,0.0002,0.0344</t>
+  </si>
+  <si>
+    <t>0.9722,0.0025,0.0025,0.0179</t>
+  </si>
+  <si>
+    <t>0.3795,0.3942,0.2955,0.0228</t>
+  </si>
+  <si>
+    <t>0.9552,0.0195,0.0259,0.0023</t>
+  </si>
+  <si>
+    <t>0.9786,0.0228,0.0032,0.0004</t>
+  </si>
+  <si>
+    <t>0.1237,0.8857,0.0441,0.0031</t>
+  </si>
+  <si>
+    <t>0.8599,0.0839,0.0766,0.0066</t>
+  </si>
+  <si>
+    <t>0.9918,0.0054,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.9976,0.0006,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9968,0.0010,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9937,0.0026,0.0013,0.0006</t>
+  </si>
+  <si>
+    <t>0.9964,0.0008,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9972,0.0002,0.0001,0.0014</t>
+  </si>
+  <si>
+    <t>0.9917,0.0039,0.0010,0.0009</t>
+  </si>
+  <si>
+    <t>0.9971,0.0005,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9979,0.0003,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9491,0.0641,0.0075,0.0006</t>
+  </si>
+  <si>
+    <t>0.6994,0.4529,0.0023,0.0009</t>
+  </si>
+  <si>
+    <t>0.3829,0.7113,0.0051,0.0035</t>
+  </si>
+  <si>
+    <t>0.8055,0.0123,0.2859,0.0019</t>
+  </si>
+  <si>
+    <t>0.9869,0.0191,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9510,0.0108,0.0545,0.0012</t>
+  </si>
+  <si>
+    <t>0.9963,0.0011,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9883,0.0043,0.0017,0.0018</t>
+  </si>
+  <si>
+    <t>0.0071,0.0139,0.9933,0.0004</t>
+  </si>
+  <si>
+    <t>0.9844,0.0139,0.0032,0.0002</t>
+  </si>
+  <si>
+    <t>0.0076,0.0024,0.9941,0.0001</t>
+  </si>
+  <si>
+    <t>0.0039,0.0109,0.9924,0.0015</t>
+  </si>
+  <si>
+    <t>0.0016,0.0023,0.9964,0.0008</t>
+  </si>
+  <si>
+    <t>0.0157,0.0043,0.9818,0.0017</t>
+  </si>
+  <si>
+    <t>0.0023,0.0022,0.9960,0.0006</t>
+  </si>
+  <si>
+    <t>0.0024,0.0006,0.9968,0.0002</t>
+  </si>
+  <si>
+    <t>0.0219,0.0021,0.9857,0.0006</t>
+  </si>
+  <si>
+    <t>0.0982,0.0102,0.9250,0.0083</t>
+  </si>
+  <si>
+    <t>0.1933,0.0039,0.9230,0.0004</t>
+  </si>
+  <si>
+    <t>0.3173,0.0684,0.7624,0.0112</t>
+  </si>
+  <si>
+    <t>0.3102,0.0130,0.8236,0.0009</t>
+  </si>
+  <si>
+    <t>0.2355,0.1269,0.6772,0.0033</t>
+  </si>
+  <si>
+    <t>0.2193,0.0459,0.8169,0.0044</t>
+  </si>
+  <si>
+    <t>0.6643,0.0098,0.4702,0.0091</t>
+  </si>
+  <si>
+    <t>0.3141,0.0069,0.8449,0.0011</t>
+  </si>
+  <si>
+    <t>0.7709,0.3472,0.0095,0.0006</t>
+  </si>
+  <si>
+    <t>0.2960,0.8405,0.0037,0.0004</t>
+  </si>
+  <si>
+    <t>0.2452,0.8504,0.0044,0.0006</t>
+  </si>
+  <si>
+    <t>0.9666,0.0726,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.7867,0.3497,0.0008,0.0009</t>
+  </si>
+  <si>
+    <t>0.5306,0.0781,0.4545,0.0159</t>
+  </si>
+  <si>
+    <t>0.9532,0.0027,0.0497,0.0016</t>
+  </si>
+  <si>
+    <t>0.8402,0.0107,0.1407,0.0151</t>
+  </si>
+  <si>
+    <t>0.8403,0.0048,0.2643,0.0018</t>
+  </si>
+  <si>
+    <t>0.7438,0.0018,0.5339,0.0004</t>
+  </si>
+  <si>
+    <t>0.0102,0.0070,0.9810,0.0056</t>
+  </si>
+  <si>
+    <t>0.0816,0.0138,0.9434,0.0013</t>
+  </si>
+  <si>
+    <t>0.2176,0.0476,0.8090,0.0014</t>
+  </si>
+  <si>
+    <t>0.2823,0.0500,0.7168,0.0162</t>
+  </si>
+  <si>
+    <t>0.0031,0.0824,0.9700,0.0084</t>
+  </si>
+  <si>
+    <t>0.9977,0.0009,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9926,0.0056,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.9940,0.0030,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9979,0.0008,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9926,0.0013,0.0001,0.0021</t>
+  </si>
+  <si>
+    <t>0.9980,0.0007,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9901,0.0068,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.0067,0.0013,0.9946,0.0002</t>
+  </si>
+  <si>
+    <t>0.3240,0.0311,0.7705,0.0057</t>
+  </si>
+  <si>
+    <t>0.8529,0.0107,0.0796,0.0367</t>
+  </si>
+  <si>
+    <t>0.0193,0.0033,0.9889,0.0001</t>
+  </si>
+  <si>
+    <t>0.0106,0.0049,0.9823,0.0017</t>
+  </si>
+  <si>
+    <t>0.0455,0.0219,0.9441,0.0026</t>
+  </si>
+  <si>
+    <t>0.0096,0.0021,0.9874,0.0018</t>
+  </si>
+  <si>
+    <t>0.0021,0.0032,0.9924,0.0049</t>
+  </si>
+  <si>
+    <t>0.0228,0.0028,0.9817,0.0008</t>
+  </si>
+  <si>
+    <t>0.0043,0.0030,0.9865,0.0091</t>
+  </si>
+  <si>
+    <t>0.0474,0.0480,0.8921,0.0741</t>
+  </si>
+  <si>
+    <t>0.7282,0.0032,0.3795,0.0025</t>
+  </si>
+  <si>
+    <t>0.6991,0.0033,0.4760,0.0020</t>
+  </si>
+  <si>
+    <t>0.9103,0.0059,0.1497,0.0011</t>
+  </si>
+  <si>
+    <t>0.9956,0.0024,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9900,0.0131,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9980,0.0010,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9962,0.0019,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9950,0.0011,0.0004,0.0012</t>
+  </si>
+  <si>
+    <t>0.9978,0.0009,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9938,0.0048,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9973,0.0006,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.0312,0.0082,0.9731,0.0002</t>
+  </si>
+  <si>
+    <t>0.0248,0.0121,0.9722,0.0013</t>
+  </si>
+  <si>
+    <t>0.0521,0.0594,0.9371,0.0070</t>
+  </si>
+  <si>
+    <t>0.0242,0.0136,0.9740,0.0006</t>
+  </si>
+  <si>
+    <t>0.0125,0.0059,0.9818,0.0025</t>
+  </si>
+  <si>
+    <t>0.0111,0.0025,0.9806,0.0046</t>
+  </si>
+  <si>
+    <t>0.0245,0.0045,0.9688,0.0113</t>
+  </si>
+  <si>
+    <t>0.2256,0.0144,0.7854,0.0038</t>
+  </si>
+  <si>
+    <t>0.9145,0.0003,0.0033,0.0638</t>
+  </si>
+  <si>
+    <t>0.0473,0.0075,0.0341,0.9589</t>
+  </si>
+  <si>
+    <t>0.0763,0.0004,0.0006,0.9836</t>
+  </si>
+  <si>
+    <t>0.0021,0.0000,0.0003,0.9991</t>
+  </si>
+  <si>
+    <t>0.0007,0.0008,0.0034,0.9985</t>
+  </si>
+  <si>
+    <t>0.9268,0.0051,0.0088,0.0570</t>
   </si>
 </sst>
 </file>
@@ -1953,7 +1953,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1978,10 +1978,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2009,7 +2009,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2023,7 +2023,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2037,7 +2037,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2051,7 +2051,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2065,7 +2065,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2079,7 +2079,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2093,7 +2093,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2107,7 +2107,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2118,10 +2118,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,7 +2177,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2233,7 +2233,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2247,7 +2247,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2258,10 +2258,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2272,10 +2272,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2345,7 +2345,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2370,10 +2370,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2387,7 +2387,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2398,10 +2398,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2415,7 +2415,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,7 +2429,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2440,10 +2440,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,7 +2527,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,7 +2569,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2625,7 +2625,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2639,7 +2639,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2681,7 +2681,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2709,7 +2709,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2723,7 +2723,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2737,7 +2737,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2765,7 +2765,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2779,7 +2779,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2793,7 +2793,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2807,7 +2807,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2821,7 +2821,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2863,7 +2863,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2891,7 +2891,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,7 +2905,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,7 +2919,7 @@
         <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2944,10 +2944,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2958,10 +2958,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,7 +2975,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2989,7 +2989,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3098,10 +3098,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3112,10 +3112,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,7 +3157,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3171,7 +3171,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3185,7 +3185,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3199,7 +3199,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3213,7 +3213,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3227,7 +3227,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>323</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3241,7 +3241,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3255,7 +3255,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3269,7 +3269,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3283,7 +3283,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3297,7 +3297,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3311,7 +3311,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3325,7 +3325,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3339,7 +3339,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3353,7 +3353,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3367,7 +3367,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>277</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3381,7 +3381,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3546,7 +3546,7 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
         <v>378</v>
@@ -3560,7 +3560,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3588,7 +3588,7 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D119" t="s">
         <v>381</v>
@@ -3602,7 +3602,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3700,7 +3700,7 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
         <v>389</v>
@@ -3773,7 +3773,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>359</v>
+        <v>394</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3787,7 +3787,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3801,7 +3801,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3815,7 +3815,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3826,10 +3826,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,7 +3843,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3885,7 +3885,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3896,10 +3896,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,7 +3927,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4011,7 +4011,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4039,7 +4039,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,7 +4053,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4067,7 +4067,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4078,10 +4078,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4095,7 +4095,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4109,7 +4109,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4120,10 +4120,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4137,7 +4137,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4148,10 +4148,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D159" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4165,7 +4165,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4179,7 +4179,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,7 +4193,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4207,7 +4207,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4221,7 +4221,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4235,7 +4235,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4249,7 +4249,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4263,7 +4263,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4277,7 +4277,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4291,7 +4291,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4305,7 +4305,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4319,7 +4319,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4333,7 +4333,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,7 +4347,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4358,10 +4358,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,7 +4375,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,7 +4389,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4403,7 +4403,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4417,7 +4417,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4431,7 +4431,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4445,7 +4445,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4459,7 +4459,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4473,7 +4473,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4487,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4529,7 +4529,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4557,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4571,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,7 +4585,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,7 +4599,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,7 +4613,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,7 +4655,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4666,10 +4666,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,7 +4683,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,7 +4711,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4722,10 +4722,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4739,7 +4739,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,7 +4753,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,7 +4767,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4781,7 +4781,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4795,7 +4795,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4806,10 +4806,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4820,10 +4820,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D207" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4907,7 +4907,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4921,7 +4921,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4935,7 +4935,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4949,7 +4949,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4963,7 +4963,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4977,7 +4977,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4991,7 +4991,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5005,7 +5005,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>481</v>
+        <v>277</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5170,7 +5170,7 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D232" t="s">
         <v>493</v>
@@ -5198,7 +5198,7 @@
         <v>259</v>
       </c>
       <c r="C234" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D234" t="s">
         <v>495</v>
